--- a/jogos_2025-07-22.xlsx
+++ b/jogos_2025-07-22.xlsx
@@ -154,15 +154,15 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Anyang</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Anyang</t>
-  </si>
-  <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>Operário PR</t>
   </si>
   <si>
@@ -175,13 +175,13 @@
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Daegu</t>
+  </si>
+  <si>
+    <t>Suwon</t>
+  </si>
+  <si>
     <t>Sangju Sangmu</t>
-  </si>
-  <si>
-    <t>Daegu</t>
-  </si>
-  <si>
-    <t>Suwon</t>
   </si>
   <si>
     <t>Atlético GO</t>
@@ -717,76 +717,76 @@
         <v>60</v>
       </c>
       <c r="L2">
-        <v>2.56</v>
+        <v>2.04</v>
       </c>
       <c r="M2">
-        <v>3.06</v>
+        <v>3.49</v>
       </c>
       <c r="N2">
-        <v>2.48</v>
+        <v>3.65</v>
       </c>
       <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>1.88</v>
+      </c>
+      <c r="AC2">
         <v>1.95</v>
       </c>
-      <c r="P2">
-        <v>8.5</v>
-      </c>
-      <c r="Q2">
-        <v>1.95</v>
-      </c>
-      <c r="R2">
-        <v>1.4</v>
-      </c>
-      <c r="S2">
-        <v>2.75</v>
-      </c>
-      <c r="T2">
-        <v>2.75</v>
-      </c>
-      <c r="U2">
-        <v>1.4</v>
-      </c>
-      <c r="V2">
-        <v>8</v>
-      </c>
-      <c r="W2">
-        <v>1.08</v>
-      </c>
-      <c r="X2">
-        <v>1.06</v>
-      </c>
-      <c r="Y2">
-        <v>8.5</v>
-      </c>
-      <c r="Z2">
-        <v>1.31</v>
-      </c>
-      <c r="AA2">
-        <v>3.45</v>
-      </c>
-      <c r="AB2">
-        <v>1.91</v>
-      </c>
-      <c r="AC2">
-        <v>1.79</v>
-      </c>
       <c r="AD2">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>6.66</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="s">
         <v>61</v>
@@ -833,13 +833,13 @@
         <v>60</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -881,10 +881,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -949,76 +949,76 @@
         <v>60</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ4" t="s">
         <v>61</v>

--- a/jogos_2025-07-22.xlsx
+++ b/jogos_2025-07-22.xlsx
@@ -154,15 +154,15 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Anyang</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
     <t>Operário PR</t>
   </si>
   <si>
@@ -175,13 +175,13 @@
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
+    <t>Suwon</t>
+  </si>
+  <si>
     <t>Daegu</t>
-  </si>
-  <si>
-    <t>Suwon</t>
-  </si>
-  <si>
-    <t>Sangju Sangmu</t>
   </si>
   <si>
     <t>Atlético GO</t>
@@ -717,76 +717,76 @@
         <v>60</v>
       </c>
       <c r="L2">
-        <v>2.04</v>
+        <v>2.56</v>
       </c>
       <c r="M2">
-        <v>3.49</v>
+        <v>3.06</v>
       </c>
       <c r="N2">
-        <v>3.65</v>
+        <v>2.48</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB2">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AC2">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ2" t="s">
         <v>61</v>
@@ -836,10 +836,10 @@
         <v>1.95</v>
       </c>
       <c r="M3">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="N3">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -881,10 +881,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC3">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -949,76 +949,76 @@
         <v>60</v>
       </c>
       <c r="L4">
-        <v>2.56</v>
+        <v>1.95</v>
       </c>
       <c r="M4">
-        <v>3.06</v>
+        <v>3.45</v>
       </c>
       <c r="N4">
-        <v>2.48</v>
+        <v>3.6</v>
       </c>
       <c r="O4">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AC4">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AD4">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>6.66</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="s">
         <v>61</v>
@@ -1065,28 +1065,28 @@
         <v>60</v>
       </c>
       <c r="L5">
-        <v>2.26</v>
+        <v>2.64</v>
       </c>
       <c r="M5">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R5">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S5">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="T5">
         <v>3.6</v>
@@ -1101,40 +1101,40 @@
         <v>1.02</v>
       </c>
       <c r="X5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y5">
         <v>5.75</v>
       </c>
       <c r="Z5">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AA5">
         <v>2.3</v>
       </c>
       <c r="AB5">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AC5">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AD5">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
         <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH5">
         <v>10</v>
       </c>
       <c r="AI5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ5" t="s">
         <v>61</v>

--- a/jogos_2025-07-22.xlsx
+++ b/jogos_2025-07-22.xlsx
@@ -154,15 +154,15 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Anyang</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Anyang</t>
-  </si>
-  <si>
     <t>Operário PR</t>
   </si>
   <si>
@@ -175,13 +175,13 @@
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Daegu</t>
+  </si>
+  <si>
+    <t>Suwon</t>
+  </si>
+  <si>
     <t>Sangju Sangmu</t>
-  </si>
-  <si>
-    <t>Suwon</t>
-  </si>
-  <si>
-    <t>Daegu</t>
   </si>
   <si>
     <t>Atlético GO</t>
@@ -717,76 +717,76 @@
         <v>60</v>
       </c>
       <c r="L2">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="M2">
-        <v>3.06</v>
+        <v>3.32</v>
       </c>
       <c r="N2">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="O2">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="P2">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q2">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="R2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S2">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="T2">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U2">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V2">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Z2">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AA2">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AB2">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AC2">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AD2">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AE2">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AF2">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG2">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH2">
-        <v>6.66</v>
+        <v>5.75</v>
       </c>
       <c r="AI2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ2" t="s">
         <v>61</v>
@@ -833,76 +833,76 @@
         <v>60</v>
       </c>
       <c r="L3">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="M3">
+        <v>3.29</v>
+      </c>
+      <c r="N3">
         <v>3.45</v>
       </c>
-      <c r="N3">
-        <v>3.6</v>
-      </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB3">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC3">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ3" t="s">
         <v>61</v>
@@ -949,76 +949,76 @@
         <v>60</v>
       </c>
       <c r="L4">
+        <v>2.56</v>
+      </c>
+      <c r="M4">
+        <v>3.06</v>
+      </c>
+      <c r="N4">
+        <v>2.48</v>
+      </c>
+      <c r="O4">
         <v>1.95</v>
       </c>
-      <c r="M4">
+      <c r="P4">
+        <v>8.5</v>
+      </c>
+      <c r="Q4">
+        <v>1.95</v>
+      </c>
+      <c r="R4">
+        <v>1.4</v>
+      </c>
+      <c r="S4">
+        <v>2.75</v>
+      </c>
+      <c r="T4">
+        <v>2.75</v>
+      </c>
+      <c r="U4">
+        <v>1.4</v>
+      </c>
+      <c r="V4">
+        <v>8</v>
+      </c>
+      <c r="W4">
+        <v>1.08</v>
+      </c>
+      <c r="X4">
+        <v>1.06</v>
+      </c>
+      <c r="Y4">
+        <v>8.5</v>
+      </c>
+      <c r="Z4">
+        <v>1.31</v>
+      </c>
+      <c r="AA4">
         <v>3.45</v>
       </c>
-      <c r="N4">
-        <v>3.6</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
       <c r="AB4">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AC4">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ4" t="s">
         <v>61</v>
@@ -1065,13 +1065,13 @@
         <v>60</v>
       </c>
       <c r="L5">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="M5">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N5">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
         <v>2</v>
@@ -1086,7 +1086,7 @@
         <v>1.6</v>
       </c>
       <c r="S5">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="T5">
         <v>3.6</v>
@@ -1101,40 +1101,40 @@
         <v>1.02</v>
       </c>
       <c r="X5">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Y5">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="Z5">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AA5">
         <v>2.3</v>
       </c>
       <c r="AB5">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AC5">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AD5">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
         <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH5">
         <v>10</v>
       </c>
       <c r="AI5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ5" t="s">
         <v>61</v>
@@ -1297,13 +1297,13 @@
         <v>60</v>
       </c>
       <c r="L7">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="M7">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>3.73</v>
       </c>
       <c r="O7">
         <v>0</v>

--- a/jogos_2025-07-22.xlsx
+++ b/jogos_2025-07-22.xlsx
@@ -154,12 +154,12 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Anyang</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>Gwangju</t>
   </si>
   <si>
@@ -175,10 +175,10 @@
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Suwon</t>
+  </si>
+  <si>
     <t>Daegu</t>
-  </si>
-  <si>
-    <t>Suwon</t>
   </si>
   <si>
     <t>Sangju Sangmu</t>
@@ -720,73 +720,73 @@
         <v>1.9</v>
       </c>
       <c r="M2">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="N2">
         <v>3.45</v>
       </c>
       <c r="O2">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="P2">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q2">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="T2">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="U2">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V2">
+        <v>7.5</v>
+      </c>
+      <c r="W2">
+        <v>1.08</v>
+      </c>
+      <c r="X2">
+        <v>1.06</v>
+      </c>
+      <c r="Y2">
+        <v>8.5</v>
+      </c>
+      <c r="Z2">
+        <v>1.33</v>
+      </c>
+      <c r="AA2">
+        <v>3.25</v>
+      </c>
+      <c r="AB2">
+        <v>1.96</v>
+      </c>
+      <c r="AC2">
+        <v>1.74</v>
+      </c>
+      <c r="AD2">
+        <v>3.5</v>
+      </c>
+      <c r="AE2">
+        <v>1.28</v>
+      </c>
+      <c r="AF2">
+        <v>1.83</v>
+      </c>
+      <c r="AG2">
+        <v>1.85</v>
+      </c>
+      <c r="AH2">
         <v>6.5</v>
       </c>
-      <c r="W2">
+      <c r="AI2">
         <v>1.1</v>
-      </c>
-      <c r="X2">
-        <v>1.05</v>
-      </c>
-      <c r="Y2">
-        <v>9</v>
-      </c>
-      <c r="Z2">
-        <v>1.28</v>
-      </c>
-      <c r="AA2">
-        <v>3.6</v>
-      </c>
-      <c r="AB2">
-        <v>1.75</v>
-      </c>
-      <c r="AC2">
-        <v>1.85</v>
-      </c>
-      <c r="AD2">
-        <v>3</v>
-      </c>
-      <c r="AE2">
-        <v>1.34</v>
-      </c>
-      <c r="AF2">
-        <v>1.7</v>
-      </c>
-      <c r="AG2">
-        <v>2</v>
-      </c>
-      <c r="AH2">
-        <v>5.75</v>
-      </c>
-      <c r="AI2">
-        <v>1.12</v>
       </c>
       <c r="AJ2" t="s">
         <v>61</v>
@@ -836,73 +836,73 @@
         <v>1.9</v>
       </c>
       <c r="M3">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="N3">
         <v>3.45</v>
       </c>
       <c r="O3">
+        <v>1.71</v>
+      </c>
+      <c r="P3">
+        <v>9.5</v>
+      </c>
+      <c r="Q3">
+        <v>2.35</v>
+      </c>
+      <c r="R3">
+        <v>1.36</v>
+      </c>
+      <c r="S3">
+        <v>2.87</v>
+      </c>
+      <c r="T3">
+        <v>2.6</v>
+      </c>
+      <c r="U3">
+        <v>1.44</v>
+      </c>
+      <c r="V3">
+        <v>6.5</v>
+      </c>
+      <c r="W3">
+        <v>1.1</v>
+      </c>
+      <c r="X3">
+        <v>1.05</v>
+      </c>
+      <c r="Y3">
+        <v>9</v>
+      </c>
+      <c r="Z3">
+        <v>1.28</v>
+      </c>
+      <c r="AA3">
+        <v>3.6</v>
+      </c>
+      <c r="AB3">
+        <v>1.75</v>
+      </c>
+      <c r="AC3">
+        <v>1.85</v>
+      </c>
+      <c r="AD3">
+        <v>3</v>
+      </c>
+      <c r="AE3">
+        <v>1.34</v>
+      </c>
+      <c r="AF3">
         <v>1.7</v>
       </c>
-      <c r="P3">
-        <v>8.5</v>
-      </c>
-      <c r="Q3">
-        <v>2.45</v>
-      </c>
-      <c r="R3">
-        <v>1.4</v>
-      </c>
-      <c r="S3">
-        <v>2.7</v>
-      </c>
-      <c r="T3">
-        <v>2.85</v>
-      </c>
-      <c r="U3">
-        <v>1.37</v>
-      </c>
-      <c r="V3">
-        <v>7.5</v>
-      </c>
-      <c r="W3">
-        <v>1.08</v>
-      </c>
-      <c r="X3">
-        <v>1.06</v>
-      </c>
-      <c r="Y3">
-        <v>8.5</v>
-      </c>
-      <c r="Z3">
-        <v>1.33</v>
-      </c>
-      <c r="AA3">
-        <v>3.25</v>
-      </c>
-      <c r="AB3">
-        <v>1.96</v>
-      </c>
-      <c r="AC3">
-        <v>1.74</v>
-      </c>
-      <c r="AD3">
-        <v>3.5</v>
-      </c>
-      <c r="AE3">
-        <v>1.28</v>
-      </c>
-      <c r="AF3">
-        <v>1.83</v>
-      </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH3">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI3">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ3" t="s">
         <v>61</v>
@@ -1065,13 +1065,13 @@
         <v>60</v>
       </c>
       <c r="L5">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="M5">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="O5">
         <v>2</v>
@@ -1083,13 +1083,13 @@
         <v>2.25</v>
       </c>
       <c r="R5">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S5">
         <v>2.25</v>
       </c>
       <c r="T5">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="U5">
         <v>1.25</v>
@@ -1104,7 +1104,7 @@
         <v>1.06</v>
       </c>
       <c r="Y5">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="Z5">
         <v>1.5</v>
@@ -1122,7 +1122,7 @@
         <v>4.75</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
         <v>2.1</v>
@@ -1131,7 +1131,7 @@
         <v>1.65</v>
       </c>
       <c r="AH5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI5">
         <v>1.02</v>
@@ -1181,13 +1181,13 @@
         <v>60</v>
       </c>
       <c r="L6">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M6">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="N6">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1229,10 +1229,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC6">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1297,13 +1297,13 @@
         <v>60</v>
       </c>
       <c r="L7">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="M7">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="N7">
-        <v>3.73</v>
+        <v>3.33</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1339,16 +1339,16 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AA7">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1413,13 +1413,13 @@
         <v>60</v>
       </c>
       <c r="L8">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="M8">
-        <v>3.5</v>
+        <v>2.83</v>
       </c>
       <c r="N8">
-        <v>4.25</v>
+        <v>3.69</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1461,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AC8">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AD8">
         <v>0</v>

--- a/jogos_2025-07-22.xlsx
+++ b/jogos_2025-07-22.xlsx
@@ -154,15 +154,15 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Anyang</t>
+  </si>
+  <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
-    <t>Anyang</t>
-  </si>
-  <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
     <t>Operário PR</t>
   </si>
   <si>
@@ -175,13 +175,13 @@
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Daegu</t>
+  </si>
+  <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
     <t>Suwon</t>
-  </si>
-  <si>
-    <t>Daegu</t>
-  </si>
-  <si>
-    <t>Sangju Sangmu</t>
   </si>
   <si>
     <t>Atlético GO</t>
@@ -720,73 +720,73 @@
         <v>1.9</v>
       </c>
       <c r="M2">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="N2">
         <v>3.45</v>
       </c>
       <c r="O2">
+        <v>1.71</v>
+      </c>
+      <c r="P2">
+        <v>9.5</v>
+      </c>
+      <c r="Q2">
+        <v>2.35</v>
+      </c>
+      <c r="R2">
+        <v>1.36</v>
+      </c>
+      <c r="S2">
+        <v>2.87</v>
+      </c>
+      <c r="T2">
+        <v>2.6</v>
+      </c>
+      <c r="U2">
+        <v>1.44</v>
+      </c>
+      <c r="V2">
+        <v>6.5</v>
+      </c>
+      <c r="W2">
+        <v>1.1</v>
+      </c>
+      <c r="X2">
+        <v>1.05</v>
+      </c>
+      <c r="Y2">
+        <v>9</v>
+      </c>
+      <c r="Z2">
+        <v>1.28</v>
+      </c>
+      <c r="AA2">
+        <v>3.6</v>
+      </c>
+      <c r="AB2">
+        <v>1.75</v>
+      </c>
+      <c r="AC2">
+        <v>1.85</v>
+      </c>
+      <c r="AD2">
+        <v>3</v>
+      </c>
+      <c r="AE2">
+        <v>1.34</v>
+      </c>
+      <c r="AF2">
         <v>1.7</v>
       </c>
-      <c r="P2">
-        <v>8.5</v>
-      </c>
-      <c r="Q2">
-        <v>2.45</v>
-      </c>
-      <c r="R2">
-        <v>1.4</v>
-      </c>
-      <c r="S2">
-        <v>2.7</v>
-      </c>
-      <c r="T2">
-        <v>2.85</v>
-      </c>
-      <c r="U2">
-        <v>1.37</v>
-      </c>
-      <c r="V2">
-        <v>7.5</v>
-      </c>
-      <c r="W2">
-        <v>1.08</v>
-      </c>
-      <c r="X2">
-        <v>1.06</v>
-      </c>
-      <c r="Y2">
-        <v>8.5</v>
-      </c>
-      <c r="Z2">
-        <v>1.33</v>
-      </c>
-      <c r="AA2">
-        <v>3.25</v>
-      </c>
-      <c r="AB2">
-        <v>1.96</v>
-      </c>
-      <c r="AC2">
-        <v>1.74</v>
-      </c>
-      <c r="AD2">
-        <v>3.5</v>
-      </c>
-      <c r="AE2">
-        <v>1.28</v>
-      </c>
-      <c r="AF2">
-        <v>1.83</v>
-      </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH2">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI2">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ2" t="s">
         <v>61</v>
@@ -833,76 +833,76 @@
         <v>60</v>
       </c>
       <c r="L3">
-        <v>1.9</v>
+        <v>2.56</v>
       </c>
       <c r="M3">
-        <v>3.32</v>
+        <v>3.06</v>
       </c>
       <c r="N3">
+        <v>2.48</v>
+      </c>
+      <c r="O3">
+        <v>1.95</v>
+      </c>
+      <c r="P3">
+        <v>8.5</v>
+      </c>
+      <c r="Q3">
+        <v>1.95</v>
+      </c>
+      <c r="R3">
+        <v>1.4</v>
+      </c>
+      <c r="S3">
+        <v>2.75</v>
+      </c>
+      <c r="T3">
+        <v>2.75</v>
+      </c>
+      <c r="U3">
+        <v>1.4</v>
+      </c>
+      <c r="V3">
+        <v>8</v>
+      </c>
+      <c r="W3">
+        <v>1.08</v>
+      </c>
+      <c r="X3">
+        <v>1.06</v>
+      </c>
+      <c r="Y3">
+        <v>8.5</v>
+      </c>
+      <c r="Z3">
+        <v>1.31</v>
+      </c>
+      <c r="AA3">
         <v>3.45</v>
       </c>
-      <c r="O3">
-        <v>1.71</v>
-      </c>
-      <c r="P3">
-        <v>9.5</v>
-      </c>
-      <c r="Q3">
-        <v>2.35</v>
-      </c>
-      <c r="R3">
-        <v>1.36</v>
-      </c>
-      <c r="S3">
-        <v>2.87</v>
-      </c>
-      <c r="T3">
-        <v>2.6</v>
-      </c>
-      <c r="U3">
-        <v>1.44</v>
-      </c>
-      <c r="V3">
-        <v>6.5</v>
-      </c>
-      <c r="W3">
-        <v>1.1</v>
-      </c>
-      <c r="X3">
-        <v>1.05</v>
-      </c>
-      <c r="Y3">
-        <v>9</v>
-      </c>
-      <c r="Z3">
-        <v>1.28</v>
-      </c>
-      <c r="AA3">
-        <v>3.6</v>
-      </c>
       <c r="AB3">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AC3">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AD3">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="AE3">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AF3">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH3">
-        <v>5.75</v>
+        <v>6.66</v>
       </c>
       <c r="AI3">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AJ3" t="s">
         <v>61</v>
@@ -949,37 +949,37 @@
         <v>60</v>
       </c>
       <c r="L4">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="M4">
-        <v>3.06</v>
+        <v>3.29</v>
       </c>
       <c r="N4">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="O4">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="P4">
         <v>8.5</v>
       </c>
       <c r="Q4">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="R4">
         <v>1.4</v>
       </c>
       <c r="S4">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T4">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U4">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W4">
         <v>1.08</v>
@@ -991,34 +991,34 @@
         <v>8.5</v>
       </c>
       <c r="Z4">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AA4">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AB4">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AC4">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AD4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AE4">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH4">
-        <v>6.66</v>
+        <v>6.5</v>
       </c>
       <c r="AI4">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ4" t="s">
         <v>61</v>
@@ -1104,7 +1104,7 @@
         <v>1.06</v>
       </c>
       <c r="Y5">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z5">
         <v>1.5</v>
@@ -1119,19 +1119,19 @@
         <v>1.44</v>
       </c>
       <c r="AD5">
-        <v>4.75</v>
+        <v>5.15</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF5">
         <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AI5">
         <v>1.02</v>
@@ -1199,58 +1199,58 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB6">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="s">
         <v>61</v>
@@ -1315,28 +1315,28 @@
         <v>0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z7">
         <v>1.48</v>
@@ -1351,22 +1351,22 @@
         <v>1.49</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ7" t="s">
         <v>61</v>
@@ -1431,34 +1431,34 @@
         <v>0</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB8">
         <v>2.3</v>
@@ -1467,22 +1467,22 @@
         <v>1.5</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ8" t="s">
         <v>61</v>

--- a/jogos_2025-07-22.xlsx
+++ b/jogos_2025-07-22.xlsx
@@ -154,15 +154,15 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Anyang</t>
   </si>
   <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>Operário PR</t>
   </si>
   <si>
@@ -175,13 +175,13 @@
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Suwon</t>
+  </si>
+  <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
     <t>Daegu</t>
-  </si>
-  <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
-    <t>Suwon</t>
   </si>
   <si>
     <t>Atlético GO</t>
@@ -720,73 +720,73 @@
         <v>1.9</v>
       </c>
       <c r="M2">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="N2">
         <v>3.45</v>
       </c>
       <c r="O2">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="P2">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q2">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="T2">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="U2">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V2">
+        <v>7.5</v>
+      </c>
+      <c r="W2">
+        <v>1.08</v>
+      </c>
+      <c r="X2">
+        <v>1.06</v>
+      </c>
+      <c r="Y2">
+        <v>8.5</v>
+      </c>
+      <c r="Z2">
+        <v>1.33</v>
+      </c>
+      <c r="AA2">
+        <v>3.25</v>
+      </c>
+      <c r="AB2">
+        <v>1.96</v>
+      </c>
+      <c r="AC2">
+        <v>1.74</v>
+      </c>
+      <c r="AD2">
+        <v>3.5</v>
+      </c>
+      <c r="AE2">
+        <v>1.28</v>
+      </c>
+      <c r="AF2">
+        <v>1.83</v>
+      </c>
+      <c r="AG2">
+        <v>1.85</v>
+      </c>
+      <c r="AH2">
         <v>6.5</v>
       </c>
-      <c r="W2">
+      <c r="AI2">
         <v>1.1</v>
-      </c>
-      <c r="X2">
-        <v>1.05</v>
-      </c>
-      <c r="Y2">
-        <v>9</v>
-      </c>
-      <c r="Z2">
-        <v>1.28</v>
-      </c>
-      <c r="AA2">
-        <v>3.6</v>
-      </c>
-      <c r="AB2">
-        <v>1.75</v>
-      </c>
-      <c r="AC2">
-        <v>1.85</v>
-      </c>
-      <c r="AD2">
-        <v>3</v>
-      </c>
-      <c r="AE2">
-        <v>1.34</v>
-      </c>
-      <c r="AF2">
-        <v>1.7</v>
-      </c>
-      <c r="AG2">
-        <v>2</v>
-      </c>
-      <c r="AH2">
-        <v>5.75</v>
-      </c>
-      <c r="AI2">
-        <v>1.12</v>
       </c>
       <c r="AJ2" t="s">
         <v>61</v>
@@ -952,73 +952,73 @@
         <v>1.9</v>
       </c>
       <c r="M4">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="N4">
         <v>3.45</v>
       </c>
       <c r="O4">
+        <v>1.71</v>
+      </c>
+      <c r="P4">
+        <v>9.5</v>
+      </c>
+      <c r="Q4">
+        <v>2.35</v>
+      </c>
+      <c r="R4">
+        <v>1.36</v>
+      </c>
+      <c r="S4">
+        <v>2.87</v>
+      </c>
+      <c r="T4">
+        <v>2.6</v>
+      </c>
+      <c r="U4">
+        <v>1.44</v>
+      </c>
+      <c r="V4">
+        <v>6.5</v>
+      </c>
+      <c r="W4">
+        <v>1.1</v>
+      </c>
+      <c r="X4">
+        <v>1.05</v>
+      </c>
+      <c r="Y4">
+        <v>9</v>
+      </c>
+      <c r="Z4">
+        <v>1.28</v>
+      </c>
+      <c r="AA4">
+        <v>3.6</v>
+      </c>
+      <c r="AB4">
+        <v>1.75</v>
+      </c>
+      <c r="AC4">
+        <v>1.85</v>
+      </c>
+      <c r="AD4">
+        <v>3</v>
+      </c>
+      <c r="AE4">
+        <v>1.34</v>
+      </c>
+      <c r="AF4">
         <v>1.7</v>
       </c>
-      <c r="P4">
-        <v>8.5</v>
-      </c>
-      <c r="Q4">
-        <v>2.45</v>
-      </c>
-      <c r="R4">
-        <v>1.4</v>
-      </c>
-      <c r="S4">
-        <v>2.7</v>
-      </c>
-      <c r="T4">
-        <v>2.85</v>
-      </c>
-      <c r="U4">
-        <v>1.37</v>
-      </c>
-      <c r="V4">
-        <v>7.5</v>
-      </c>
-      <c r="W4">
-        <v>1.08</v>
-      </c>
-      <c r="X4">
-        <v>1.06</v>
-      </c>
-      <c r="Y4">
-        <v>8.5</v>
-      </c>
-      <c r="Z4">
-        <v>1.33</v>
-      </c>
-      <c r="AA4">
-        <v>3.25</v>
-      </c>
-      <c r="AB4">
-        <v>1.96</v>
-      </c>
-      <c r="AC4">
-        <v>1.74</v>
-      </c>
-      <c r="AD4">
-        <v>3.5</v>
-      </c>
-      <c r="AE4">
-        <v>1.28</v>
-      </c>
-      <c r="AF4">
-        <v>1.83</v>
-      </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH4">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI4">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ4" t="s">
         <v>61</v>
@@ -1089,22 +1089,22 @@
         <v>2.25</v>
       </c>
       <c r="T5">
-        <v>3.66</v>
+        <v>3.95</v>
       </c>
       <c r="U5">
         <v>1.25</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W5">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
         <v>1.06</v>
       </c>
       <c r="Y5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>1.5</v>
@@ -1113,25 +1113,25 @@
         <v>2.3</v>
       </c>
       <c r="AB5">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AC5">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AD5">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
         <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AI5">
         <v>1.02</v>
@@ -1190,13 +1190,13 @@
         <v>6.6</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R6">
         <v>1.39</v>
@@ -1211,16 +1211,16 @@
         <v>1.34</v>
       </c>
       <c r="V6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>1.02</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>9.15</v>
       </c>
       <c r="Z6">
         <v>1.33</v>
@@ -1235,19 +1235,19 @@
         <v>1.75</v>
       </c>
       <c r="AD6">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AE6">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF6">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG6">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH6">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AI6">
         <v>1.08</v>
@@ -1306,13 +1306,13 @@
         <v>3.33</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R7">
         <v>1.55</v>
@@ -1324,16 +1324,16 @@
         <v>3.4</v>
       </c>
       <c r="U7">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
         <v>6.5</v>
@@ -1351,19 +1351,19 @@
         <v>1.49</v>
       </c>
       <c r="AD7">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE7">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF7">
         <v>2.1</v>
       </c>
       <c r="AG7">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH7">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AI7">
         <v>1.05</v>
@@ -1422,31 +1422,31 @@
         <v>3.69</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R8">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S8">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T8">
         <v>3.4</v>
       </c>
       <c r="U8">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X8">
         <v>1.1</v>
@@ -1458,7 +1458,7 @@
         <v>1.44</v>
       </c>
       <c r="AA8">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AB8">
         <v>2.3</v>
@@ -1467,19 +1467,19 @@
         <v>1.5</v>
       </c>
       <c r="AD8">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AE8">
         <v>1.17</v>
       </c>
       <c r="AF8">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AG8">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AI8">
         <v>1.05</v>

--- a/jogos_2025-07-22.xlsx
+++ b/jogos_2025-07-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -133,6 +133,27 @@
     <t>07:30</t>
   </si>
   <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
     <t>19:00</t>
   </si>
   <si>
@@ -148,19 +169,64 @@
     <t>South Korea K League 1</t>
   </si>
   <si>
+    <t>Europe UEFA Champions League</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
     <t>2025</t>
   </si>
   <si>
+    <t>2025/2026</t>
+  </si>
+  <si>
+    <t>Anyang</t>
+  </si>
+  <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
-    <t>Anyang</t>
+    <t>KuPS</t>
+  </si>
+  <si>
+    <t>Artsakh</t>
+  </si>
+  <si>
+    <t>Lincoln Red Imps</t>
+  </si>
+  <si>
+    <t>København</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Hamrun Spartans</t>
+  </si>
+  <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
+    <t>Shkendija</t>
+  </si>
+  <si>
+    <t>Slovan Bratislava</t>
+  </si>
+  <si>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
+    <t>Rangers</t>
   </si>
   <si>
     <t>Operário PR</t>
@@ -175,13 +241,52 @@
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Daegu</t>
+  </si>
+  <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
     <t>Suwon</t>
   </si>
   <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
-    <t>Daegu</t>
+    <t>Kairat</t>
+  </si>
+  <si>
+    <t>Ferencváros</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Drita</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Dynamo Kyiv</t>
+  </si>
+  <si>
+    <t>Malmö FF</t>
+  </si>
+  <si>
+    <t>FCSB</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Breidablik</t>
+  </si>
+  <si>
+    <t>Ludogorets</t>
+  </si>
+  <si>
+    <t>Panathinaikos</t>
   </si>
   <si>
     <t>Atlético GO</t>
@@ -563,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL8"/>
+  <dimension ref="A1:AL21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -690,16 +795,16 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -714,85 +819,85 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="L2">
         <v>1.9</v>
       </c>
       <c r="M2">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="N2">
         <v>3.45</v>
       </c>
       <c r="O2">
+        <v>1.71</v>
+      </c>
+      <c r="P2">
+        <v>9.5</v>
+      </c>
+      <c r="Q2">
+        <v>2.35</v>
+      </c>
+      <c r="R2">
+        <v>1.36</v>
+      </c>
+      <c r="S2">
+        <v>2.87</v>
+      </c>
+      <c r="T2">
+        <v>2.6</v>
+      </c>
+      <c r="U2">
+        <v>1.44</v>
+      </c>
+      <c r="V2">
+        <v>6.5</v>
+      </c>
+      <c r="W2">
+        <v>1.1</v>
+      </c>
+      <c r="X2">
+        <v>1.05</v>
+      </c>
+      <c r="Y2">
+        <v>9</v>
+      </c>
+      <c r="Z2">
+        <v>1.28</v>
+      </c>
+      <c r="AA2">
+        <v>3.6</v>
+      </c>
+      <c r="AB2">
         <v>1.7</v>
       </c>
-      <c r="P2">
-        <v>8.5</v>
-      </c>
-      <c r="Q2">
-        <v>2.45</v>
-      </c>
-      <c r="R2">
-        <v>1.4</v>
-      </c>
-      <c r="S2">
-        <v>2.7</v>
-      </c>
-      <c r="T2">
-        <v>2.85</v>
-      </c>
-      <c r="U2">
-        <v>1.37</v>
-      </c>
-      <c r="V2">
-        <v>7.5</v>
-      </c>
-      <c r="W2">
-        <v>1.08</v>
-      </c>
-      <c r="X2">
-        <v>1.06</v>
-      </c>
-      <c r="Y2">
-        <v>8.5</v>
-      </c>
-      <c r="Z2">
-        <v>1.33</v>
-      </c>
-      <c r="AA2">
-        <v>3.25</v>
-      </c>
-      <c r="AB2">
-        <v>1.96</v>
-      </c>
       <c r="AC2">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="AD2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AE2">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AF2">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH2">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI2">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ2" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="AK2" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="AL2" s="3">
         <v>45860.3125</v>
@@ -806,16 +911,16 @@
         <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -830,7 +935,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="L3">
         <v>2.56</v>
@@ -905,10 +1010,10 @@
         <v>1.11</v>
       </c>
       <c r="AJ3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="AK3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="AL3" s="3">
         <v>45860.3125</v>
@@ -922,16 +1027,16 @@
         <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -946,85 +1051,85 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="L4">
         <v>1.9</v>
       </c>
       <c r="M4">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="N4">
         <v>3.45</v>
       </c>
       <c r="O4">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="P4">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q4">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="R4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S4">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="T4">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="U4">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V4">
+        <v>7.5</v>
+      </c>
+      <c r="W4">
+        <v>1.08</v>
+      </c>
+      <c r="X4">
+        <v>1.06</v>
+      </c>
+      <c r="Y4">
+        <v>8.5</v>
+      </c>
+      <c r="Z4">
+        <v>1.33</v>
+      </c>
+      <c r="AA4">
+        <v>3.25</v>
+      </c>
+      <c r="AB4">
+        <v>1.96</v>
+      </c>
+      <c r="AC4">
+        <v>1.74</v>
+      </c>
+      <c r="AD4">
+        <v>3.5</v>
+      </c>
+      <c r="AE4">
+        <v>1.28</v>
+      </c>
+      <c r="AF4">
+        <v>1.83</v>
+      </c>
+      <c r="AG4">
+        <v>1.85</v>
+      </c>
+      <c r="AH4">
         <v>6.5</v>
       </c>
-      <c r="W4">
+      <c r="AI4">
         <v>1.1</v>
       </c>
-      <c r="X4">
-        <v>1.05</v>
-      </c>
-      <c r="Y4">
-        <v>9</v>
-      </c>
-      <c r="Z4">
-        <v>1.28</v>
-      </c>
-      <c r="AA4">
-        <v>3.6</v>
-      </c>
-      <c r="AB4">
-        <v>1.75</v>
-      </c>
-      <c r="AC4">
-        <v>1.85</v>
-      </c>
-      <c r="AD4">
-        <v>3</v>
-      </c>
-      <c r="AE4">
-        <v>1.34</v>
-      </c>
-      <c r="AF4">
-        <v>1.7</v>
-      </c>
-      <c r="AG4">
-        <v>2</v>
-      </c>
-      <c r="AH4">
-        <v>5.75</v>
-      </c>
-      <c r="AI4">
-        <v>1.12</v>
-      </c>
       <c r="AJ4" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="AK4" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="AL4" s="3">
         <v>45860.3125</v>
@@ -1038,16 +1143,16 @@
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1062,88 +1167,88 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="L5">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="M5">
-        <v>2.72</v>
+        <v>3.35</v>
       </c>
       <c r="N5">
-        <v>3.21</v>
+        <v>2.65</v>
       </c>
       <c r="O5">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="P5">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q5">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="S5">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T5">
+        <v>3.1</v>
+      </c>
+      <c r="U5">
+        <v>1.32</v>
+      </c>
+      <c r="V5">
+        <v>8.25</v>
+      </c>
+      <c r="W5">
+        <v>1.06</v>
+      </c>
+      <c r="X5">
+        <v>1.02</v>
+      </c>
+      <c r="Y5">
+        <v>7.9</v>
+      </c>
+      <c r="Z5">
+        <v>1.35</v>
+      </c>
+      <c r="AA5">
+        <v>2.83</v>
+      </c>
+      <c r="AB5">
+        <v>2.2</v>
+      </c>
+      <c r="AC5">
+        <v>1.61</v>
+      </c>
+      <c r="AD5">
         <v>3.95</v>
       </c>
-      <c r="U5">
-        <v>1.25</v>
-      </c>
-      <c r="V5">
-        <v>11</v>
-      </c>
-      <c r="W5">
-        <v>1.04</v>
-      </c>
-      <c r="X5">
-        <v>1.06</v>
-      </c>
-      <c r="Y5">
-        <v>6</v>
-      </c>
-      <c r="Z5">
-        <v>1.5</v>
-      </c>
-      <c r="AA5">
-        <v>2.3</v>
-      </c>
-      <c r="AB5">
-        <v>2.65</v>
-      </c>
-      <c r="AC5">
-        <v>1.42</v>
-      </c>
-      <c r="AD5">
-        <v>5.25</v>
-      </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF5">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AG5">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH5">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="AI5">
         <v>1.02</v>
       </c>
       <c r="AJ5" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="AK5" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="AL5" s="3">
-        <v>45860.79166666666</v>
+        <v>45860.5</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1154,16 +1259,16 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1178,88 +1283,88 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="L6">
-        <v>1.45</v>
+        <v>3.1</v>
       </c>
       <c r="M6">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N6">
-        <v>6.6</v>
+        <v>2.2</v>
       </c>
       <c r="O6">
-        <v>1.39</v>
+        <v>2.2</v>
       </c>
       <c r="P6">
         <v>8.5</v>
       </c>
       <c r="Q6">
-        <v>3.6</v>
+        <v>1.82</v>
       </c>
       <c r="R6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S6">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="T6">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="U6">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>9.15</v>
+        <v>8.5</v>
       </c>
       <c r="Z6">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AA6">
         <v>3.1</v>
       </c>
       <c r="AB6">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC6">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD6">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AE6">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AF6">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AG6">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AH6">
-        <v>7.7</v>
+        <v>6.75</v>
       </c>
       <c r="AI6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AJ6" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="AK6" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="AL6" s="3">
-        <v>45860.83333333334</v>
+        <v>45860.54166666666</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1267,19 +1372,19 @@
         <v>45860</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1294,88 +1399,88 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="L7">
-        <v>2.13</v>
+        <v>11</v>
       </c>
       <c r="M7">
-        <v>2.87</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>3.33</v>
+        <v>1.2</v>
       </c>
       <c r="O7">
-        <v>1.87</v>
+        <v>4.75</v>
       </c>
       <c r="P7">
-        <v>6.25</v>
+        <v>13.5</v>
       </c>
       <c r="Q7">
-        <v>2.37</v>
+        <v>1.23</v>
       </c>
       <c r="R7">
+        <v>1.28</v>
+      </c>
+      <c r="S7">
+        <v>3.4</v>
+      </c>
+      <c r="T7">
+        <v>2.25</v>
+      </c>
+      <c r="U7">
         <v>1.55</v>
       </c>
-      <c r="S7">
-        <v>2.3</v>
-      </c>
-      <c r="T7">
-        <v>3.4</v>
-      </c>
-      <c r="U7">
-        <v>1.25</v>
-      </c>
       <c r="V7">
-        <v>8.6</v>
+        <v>5.25</v>
       </c>
       <c r="W7">
+        <v>1.14</v>
+      </c>
+      <c r="X7">
         <v>1.01</v>
       </c>
-      <c r="X7">
-        <v>1.05</v>
-      </c>
       <c r="Y7">
-        <v>6.5</v>
+        <v>17</v>
       </c>
       <c r="Z7">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="AA7">
+        <v>4.33</v>
+      </c>
+      <c r="AB7">
+        <v>1.53</v>
+      </c>
+      <c r="AC7">
         <v>2.4</v>
       </c>
-      <c r="AB7">
-        <v>2.45</v>
-      </c>
-      <c r="AC7">
-        <v>1.49</v>
-      </c>
       <c r="AD7">
-        <v>4.75</v>
+        <v>2.34</v>
       </c>
       <c r="AE7">
+        <v>1.6</v>
+      </c>
+      <c r="AF7">
+        <v>2.25</v>
+      </c>
+      <c r="AG7">
+        <v>1.57</v>
+      </c>
+      <c r="AH7">
+        <v>4.3</v>
+      </c>
+      <c r="AI7">
         <v>1.16</v>
       </c>
-      <c r="AF7">
-        <v>2.1</v>
-      </c>
-      <c r="AG7">
-        <v>1.65</v>
-      </c>
-      <c r="AH7">
-        <v>9.5</v>
-      </c>
-      <c r="AI7">
-        <v>1.05</v>
-      </c>
       <c r="AJ7" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="AK7" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="AL7" s="3">
-        <v>45860.89583333334</v>
+        <v>45860.54166666666</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1383,114 +1488,1622 @@
         <v>45860</v>
       </c>
       <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>95</v>
+      </c>
+      <c r="L8">
+        <v>1.13</v>
+      </c>
+      <c r="M8">
+        <v>7.6</v>
+      </c>
+      <c r="N8">
+        <v>18</v>
+      </c>
+      <c r="O8">
+        <v>1.13</v>
+      </c>
+      <c r="P8">
+        <v>18.5</v>
+      </c>
+      <c r="Q8">
+        <v>6</v>
+      </c>
+      <c r="R8">
+        <v>1.2</v>
+      </c>
+      <c r="S8">
+        <v>4.33</v>
+      </c>
+      <c r="T8">
+        <v>1.91</v>
+      </c>
+      <c r="U8">
+        <v>1.8</v>
+      </c>
+      <c r="V8">
+        <v>4</v>
+      </c>
+      <c r="W8">
+        <v>1.22</v>
+      </c>
+      <c r="X8">
+        <v>1.01</v>
+      </c>
+      <c r="Y8">
+        <v>19</v>
+      </c>
+      <c r="Z8">
+        <v>1.12</v>
+      </c>
+      <c r="AA8">
+        <v>5.47</v>
+      </c>
+      <c r="AB8">
+        <v>1.42</v>
+      </c>
+      <c r="AC8">
+        <v>2.75</v>
+      </c>
+      <c r="AD8">
+        <v>1.95</v>
+      </c>
+      <c r="AE8">
+        <v>1.65</v>
+      </c>
+      <c r="AF8">
+        <v>2.25</v>
+      </c>
+      <c r="AG8">
+        <v>1.57</v>
+      </c>
+      <c r="AH8">
+        <v>3.02</v>
+      </c>
+      <c r="AI8">
+        <v>1.31</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL8" s="3">
+        <v>45860.58333333334</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38">
+      <c r="A9" s="2">
+        <v>45860</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>95</v>
+      </c>
+      <c r="L9">
+        <v>2.13</v>
+      </c>
+      <c r="M9">
+        <v>3.4</v>
+      </c>
+      <c r="N9">
+        <v>3.3</v>
+      </c>
+      <c r="O9">
+        <v>1.67</v>
+      </c>
+      <c r="P9">
+        <v>9.5</v>
+      </c>
+      <c r="Q9">
+        <v>2.4</v>
+      </c>
+      <c r="R9">
+        <v>1.36</v>
+      </c>
+      <c r="S9">
+        <v>3</v>
+      </c>
+      <c r="T9">
+        <v>2.75</v>
+      </c>
+      <c r="U9">
+        <v>1.4</v>
+      </c>
+      <c r="V9">
+        <v>6.5</v>
+      </c>
+      <c r="W9">
+        <v>1.1</v>
+      </c>
+      <c r="X9">
+        <v>1.04</v>
+      </c>
+      <c r="Y9">
+        <v>9</v>
+      </c>
+      <c r="Z9">
+        <v>1.22</v>
+      </c>
+      <c r="AA9">
+        <v>3.9</v>
+      </c>
+      <c r="AB9">
+        <v>1.88</v>
+      </c>
+      <c r="AC9">
+        <v>1.72</v>
+      </c>
+      <c r="AD9">
+        <v>2.75</v>
+      </c>
+      <c r="AE9">
+        <v>1.42</v>
+      </c>
+      <c r="AF9">
+        <v>1.8</v>
+      </c>
+      <c r="AG9">
+        <v>1.91</v>
+      </c>
+      <c r="AH9">
+        <v>4</v>
+      </c>
+      <c r="AI9">
+        <v>1.22</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL9" s="3">
+        <v>45860.58333333334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38">
+      <c r="A10" s="2">
+        <v>45860</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10">
+        <v>1.77</v>
+      </c>
+      <c r="M10">
+        <v>3.3</v>
+      </c>
+      <c r="N10">
+        <v>4.3</v>
+      </c>
+      <c r="O10">
+        <v>1.44</v>
+      </c>
+      <c r="P10">
+        <v>10</v>
+      </c>
+      <c r="Q10">
+        <v>2.88</v>
+      </c>
+      <c r="R10">
+        <v>1.33</v>
+      </c>
+      <c r="S10">
+        <v>3.25</v>
+      </c>
+      <c r="T10">
+        <v>2.63</v>
+      </c>
+      <c r="U10">
+        <v>1.44</v>
+      </c>
+      <c r="V10">
+        <v>6</v>
+      </c>
+      <c r="W10">
+        <v>1.11</v>
+      </c>
+      <c r="X10">
+        <v>1.04</v>
+      </c>
+      <c r="Y10">
+        <v>9</v>
+      </c>
+      <c r="Z10">
+        <v>1.25</v>
+      </c>
+      <c r="AA10">
+        <v>3.8</v>
+      </c>
+      <c r="AB10">
+        <v>1.75</v>
+      </c>
+      <c r="AC10">
+        <v>1.95</v>
+      </c>
+      <c r="AD10">
+        <v>2.9</v>
+      </c>
+      <c r="AE10">
+        <v>1.38</v>
+      </c>
+      <c r="AF10">
+        <v>1.8</v>
+      </c>
+      <c r="AG10">
+        <v>1.91</v>
+      </c>
+      <c r="AH10">
+        <v>5.25</v>
+      </c>
+      <c r="AI10">
+        <v>1.09</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL10" s="3">
+        <v>45860.58333333334</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38">
+      <c r="A11" s="2">
+        <v>45860</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11">
+        <v>7</v>
+      </c>
+      <c r="M11">
+        <v>4.5</v>
+      </c>
+      <c r="N11">
+        <v>1.41</v>
+      </c>
+      <c r="O11">
+        <v>3.25</v>
+      </c>
+      <c r="P11">
+        <v>13</v>
+      </c>
+      <c r="Q11">
+        <v>1.38</v>
+      </c>
+      <c r="R11">
+        <v>1.27</v>
+      </c>
+      <c r="S11">
+        <v>3.4</v>
+      </c>
+      <c r="T11">
+        <v>2.25</v>
+      </c>
+      <c r="U11">
+        <v>1.55</v>
+      </c>
+      <c r="V11">
+        <v>5.25</v>
+      </c>
+      <c r="W11">
+        <v>1.14</v>
+      </c>
+      <c r="X11">
+        <v>1.02</v>
+      </c>
+      <c r="Y11">
+        <v>13.5</v>
+      </c>
+      <c r="Z11">
+        <v>1.19</v>
+      </c>
+      <c r="AA11">
+        <v>4.33</v>
+      </c>
+      <c r="AB11">
+        <v>1.57</v>
+      </c>
+      <c r="AC11">
+        <v>2.3</v>
+      </c>
+      <c r="AD11">
+        <v>2.45</v>
+      </c>
+      <c r="AE11">
+        <v>1.49</v>
+      </c>
+      <c r="AF11">
+        <v>1.8</v>
+      </c>
+      <c r="AG11">
+        <v>1.88</v>
+      </c>
+      <c r="AH11">
+        <v>4.33</v>
+      </c>
+      <c r="AI11">
+        <v>1.2</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL11" s="3">
+        <v>45860.58333333334</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38">
+      <c r="A12" s="2">
+        <v>45860</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>95</v>
+      </c>
+      <c r="L12">
+        <v>3.75</v>
+      </c>
+      <c r="M12">
+        <v>3.4</v>
+      </c>
+      <c r="N12">
+        <v>1.97</v>
+      </c>
+      <c r="O12">
+        <v>2.2</v>
+      </c>
+      <c r="P12">
+        <v>7.75</v>
+      </c>
+      <c r="Q12">
+        <v>1.88</v>
+      </c>
+      <c r="R12">
+        <v>1.42</v>
+      </c>
+      <c r="S12">
+        <v>2.6</v>
+      </c>
+      <c r="T12">
+        <v>2.8</v>
+      </c>
+      <c r="U12">
+        <v>1.37</v>
+      </c>
+      <c r="V12">
+        <v>7.25</v>
+      </c>
+      <c r="W12">
+        <v>1.08</v>
+      </c>
+      <c r="X12">
+        <v>1.01</v>
+      </c>
+      <c r="Y12">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Z12">
+        <v>1.3</v>
+      </c>
+      <c r="AA12">
+        <v>3.08</v>
+      </c>
+      <c r="AB12">
+        <v>1.89</v>
+      </c>
+      <c r="AC12">
+        <v>1.81</v>
+      </c>
+      <c r="AD12">
+        <v>3.62</v>
+      </c>
+      <c r="AE12">
+        <v>1.22</v>
+      </c>
+      <c r="AF12">
+        <v>1.78</v>
+      </c>
+      <c r="AG12">
+        <v>1.9</v>
+      </c>
+      <c r="AH12">
+        <v>7.6</v>
+      </c>
+      <c r="AI12">
+        <v>1.03</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL12" s="3">
+        <v>45860.58333333334</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38">
+      <c r="A13" s="2">
+        <v>45860</v>
+      </c>
+      <c r="B13" t="s">
         <v>42</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>95</v>
+      </c>
+      <c r="L13">
+        <v>3.6</v>
+      </c>
+      <c r="M13">
+        <v>3.15</v>
+      </c>
+      <c r="N13">
+        <v>2.05</v>
+      </c>
+      <c r="O13">
+        <v>2.45</v>
+      </c>
+      <c r="P13">
+        <v>7</v>
+      </c>
+      <c r="Q13">
+        <v>1.75</v>
+      </c>
+      <c r="R13">
+        <v>1.47</v>
+      </c>
+      <c r="S13">
+        <v>2.45</v>
+      </c>
+      <c r="T13">
+        <v>3.1</v>
+      </c>
+      <c r="U13">
+        <v>1.31</v>
+      </c>
+      <c r="V13">
+        <v>8.5</v>
+      </c>
+      <c r="W13">
+        <v>1.06</v>
+      </c>
+      <c r="X13">
+        <v>1.08</v>
+      </c>
+      <c r="Y13">
+        <v>7.25</v>
+      </c>
+      <c r="Z13">
+        <v>1.4</v>
+      </c>
+      <c r="AA13">
+        <v>2.75</v>
+      </c>
+      <c r="AB13">
+        <v>2.2</v>
+      </c>
+      <c r="AC13">
+        <v>1.61</v>
+      </c>
+      <c r="AD13">
+        <v>4</v>
+      </c>
+      <c r="AE13">
+        <v>1.22</v>
+      </c>
+      <c r="AF13">
+        <v>1.98</v>
+      </c>
+      <c r="AG13">
+        <v>1.73</v>
+      </c>
+      <c r="AH13">
+        <v>8.25</v>
+      </c>
+      <c r="AI13">
+        <v>1.07</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>45860.625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38">
+      <c r="A14" s="2">
+        <v>45860</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L14">
+        <v>1.8</v>
+      </c>
+      <c r="M14">
+        <v>3.5</v>
+      </c>
+      <c r="N14">
+        <v>4.4</v>
+      </c>
+      <c r="O14">
+        <v>1.58</v>
+      </c>
+      <c r="P14">
+        <v>9.25</v>
+      </c>
+      <c r="Q14">
+        <v>2.65</v>
+      </c>
+      <c r="R14">
+        <v>1.36</v>
+      </c>
+      <c r="S14">
+        <v>2.85</v>
+      </c>
+      <c r="T14">
+        <v>2.65</v>
+      </c>
+      <c r="U14">
+        <v>1.42</v>
+      </c>
+      <c r="V14">
+        <v>6.5</v>
+      </c>
+      <c r="W14">
+        <v>1.09</v>
+      </c>
+      <c r="X14">
+        <v>1.05</v>
+      </c>
+      <c r="Y14">
+        <v>9.5</v>
+      </c>
+      <c r="Z14">
+        <v>1.28</v>
+      </c>
+      <c r="AA14">
+        <v>3.4</v>
+      </c>
+      <c r="AB14">
+        <v>1.78</v>
+      </c>
+      <c r="AC14">
+        <v>1.82</v>
+      </c>
+      <c r="AD14">
+        <v>3.55</v>
+      </c>
+      <c r="AE14">
+        <v>1.28</v>
+      </c>
+      <c r="AF14">
+        <v>1.8</v>
+      </c>
+      <c r="AG14">
+        <v>1.88</v>
+      </c>
+      <c r="AH14">
+        <v>5.75</v>
+      </c>
+      <c r="AI14">
+        <v>1.12</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>45860.63541666666</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38">
+      <c r="A15" s="2">
+        <v>45860</v>
+      </c>
+      <c r="B15" t="s">
         <v>44</v>
       </c>
-      <c r="D8" t="s">
+      <c r="C15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>95</v>
+      </c>
+      <c r="L15">
+        <v>1.3</v>
+      </c>
+      <c r="M15">
+        <v>6.5</v>
+      </c>
+      <c r="N15">
+        <v>6</v>
+      </c>
+      <c r="O15">
+        <v>1.31</v>
+      </c>
+      <c r="P15">
+        <v>15</v>
+      </c>
+      <c r="Q15">
+        <v>3.7</v>
+      </c>
+      <c r="R15">
+        <v>1.24</v>
+      </c>
+      <c r="S15">
+        <v>3.6</v>
+      </c>
+      <c r="T15">
+        <v>2.15</v>
+      </c>
+      <c r="U15">
+        <v>1.61</v>
+      </c>
+      <c r="V15">
+        <v>4.8</v>
+      </c>
+      <c r="W15">
+        <v>1.16</v>
+      </c>
+      <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
+        <v>15.5</v>
+      </c>
+      <c r="Z15">
+        <v>1.17</v>
+      </c>
+      <c r="AA15">
+        <v>4.75</v>
+      </c>
+      <c r="AB15">
+        <v>1.56</v>
+      </c>
+      <c r="AC15">
+        <v>2.27</v>
+      </c>
+      <c r="AD15">
+        <v>2.15</v>
+      </c>
+      <c r="AE15">
+        <v>1.65</v>
+      </c>
+      <c r="AF15">
+        <v>1.88</v>
+      </c>
+      <c r="AG15">
+        <v>1.8</v>
+      </c>
+      <c r="AH15">
+        <v>3.9</v>
+      </c>
+      <c r="AI15">
+        <v>1.22</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>45860.64583333334</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38">
+      <c r="A16" s="2">
+        <v>45860</v>
+      </c>
+      <c r="B16" t="s">
         <v>45</v>
       </c>
-      <c r="E8" t="s">
+      <c r="C16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>95</v>
+      </c>
+      <c r="L16">
+        <v>2.22</v>
+      </c>
+      <c r="M16">
+        <v>3.25</v>
+      </c>
+      <c r="N16">
+        <v>3.2</v>
+      </c>
+      <c r="O16">
+        <v>1.83</v>
+      </c>
+      <c r="P16">
+        <v>7.5</v>
+      </c>
+      <c r="Q16">
+        <v>2.3</v>
+      </c>
+      <c r="R16">
+        <v>1.44</v>
+      </c>
+      <c r="S16">
+        <v>2.55</v>
+      </c>
+      <c r="T16">
+        <v>2.95</v>
+      </c>
+      <c r="U16">
+        <v>1.34</v>
+      </c>
+      <c r="V16">
+        <v>8</v>
+      </c>
+      <c r="W16">
+        <v>1.07</v>
+      </c>
+      <c r="X16">
+        <v>1.08</v>
+      </c>
+      <c r="Y16">
+        <v>7.5</v>
+      </c>
+      <c r="Z16">
+        <v>1.37</v>
+      </c>
+      <c r="AA16">
+        <v>2.87</v>
+      </c>
+      <c r="AB16">
+        <v>2.29</v>
+      </c>
+      <c r="AC16">
+        <v>1.55</v>
+      </c>
+      <c r="AD16">
+        <v>3.7</v>
+      </c>
+      <c r="AE16">
+        <v>1.24</v>
+      </c>
+      <c r="AF16">
+        <v>1.87</v>
+      </c>
+      <c r="AG16">
+        <v>1.82</v>
+      </c>
+      <c r="AH16">
+        <v>7.5</v>
+      </c>
+      <c r="AI16">
+        <v>1.08</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL16" s="3">
+        <v>45860.65625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38">
+      <c r="A17" s="2">
+        <v>45860</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>95</v>
+      </c>
+      <c r="L17">
+        <v>1.87</v>
+      </c>
+      <c r="M17">
+        <v>3.3</v>
+      </c>
+      <c r="N17">
+        <v>3.8</v>
+      </c>
+      <c r="O17">
+        <v>1.53</v>
+      </c>
+      <c r="P17">
+        <v>10</v>
+      </c>
+      <c r="Q17">
+        <v>2.75</v>
+      </c>
+      <c r="R17">
+        <v>1.36</v>
+      </c>
+      <c r="S17">
+        <v>3</v>
+      </c>
+      <c r="T17">
+        <v>2.63</v>
+      </c>
+      <c r="U17">
+        <v>1.44</v>
+      </c>
+      <c r="V17">
+        <v>6.5</v>
+      </c>
+      <c r="W17">
+        <v>1.1</v>
+      </c>
+      <c r="X17">
+        <v>1.04</v>
+      </c>
+      <c r="Y17">
+        <v>10</v>
+      </c>
+      <c r="Z17">
+        <v>1.22</v>
+      </c>
+      <c r="AA17">
+        <v>4.2</v>
+      </c>
+      <c r="AB17">
+        <v>1.8</v>
+      </c>
+      <c r="AC17">
+        <v>1.9</v>
+      </c>
+      <c r="AD17">
+        <v>2.7</v>
+      </c>
+      <c r="AE17">
+        <v>1.45</v>
+      </c>
+      <c r="AF17">
+        <v>1.73</v>
+      </c>
+      <c r="AG17">
+        <v>2</v>
+      </c>
+      <c r="AH17">
+        <v>4.75</v>
+      </c>
+      <c r="AI17">
+        <v>1.18</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL17" s="3">
+        <v>45860.65625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38">
+      <c r="A18" s="2">
+        <v>45860</v>
+      </c>
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
         <v>52</v>
       </c>
-      <c r="F8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" t="s">
-        <v>60</v>
-      </c>
-      <c r="L8">
+      <c r="D18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" t="s">
+        <v>95</v>
+      </c>
+      <c r="L18">
+        <v>2.27</v>
+      </c>
+      <c r="M18">
+        <v>2.72</v>
+      </c>
+      <c r="N18">
+        <v>3.21</v>
+      </c>
+      <c r="O18">
+        <v>2</v>
+      </c>
+      <c r="P18">
+        <v>5.75</v>
+      </c>
+      <c r="Q18">
+        <v>2.25</v>
+      </c>
+      <c r="R18">
+        <v>1.62</v>
+      </c>
+      <c r="S18">
+        <v>2.22</v>
+      </c>
+      <c r="T18">
+        <v>3.75</v>
+      </c>
+      <c r="U18">
+        <v>1.21</v>
+      </c>
+      <c r="V18">
+        <v>10</v>
+      </c>
+      <c r="W18">
+        <v>1.02</v>
+      </c>
+      <c r="X18">
+        <v>1.13</v>
+      </c>
+      <c r="Y18">
+        <v>5.75</v>
+      </c>
+      <c r="Z18">
+        <v>1.5</v>
+      </c>
+      <c r="AA18">
+        <v>2.3</v>
+      </c>
+      <c r="AB18">
+        <v>2.65</v>
+      </c>
+      <c r="AC18">
+        <v>1.42</v>
+      </c>
+      <c r="AD18">
+        <v>5.93</v>
+      </c>
+      <c r="AE18">
+        <v>1.13</v>
+      </c>
+      <c r="AF18">
+        <v>2.2</v>
+      </c>
+      <c r="AG18">
+        <v>1.62</v>
+      </c>
+      <c r="AH18">
+        <v>13</v>
+      </c>
+      <c r="AI18">
+        <v>1.03</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL18" s="3">
+        <v>45860.79166666666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38">
+      <c r="A19" s="2">
+        <v>45860</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="s">
+        <v>95</v>
+      </c>
+      <c r="L19">
+        <v>1.45</v>
+      </c>
+      <c r="M19">
+        <v>3.6</v>
+      </c>
+      <c r="N19">
+        <v>6.6</v>
+      </c>
+      <c r="O19">
+        <v>1.39</v>
+      </c>
+      <c r="P19">
+        <v>8.5</v>
+      </c>
+      <c r="Q19">
+        <v>3.6</v>
+      </c>
+      <c r="R19">
+        <v>1.45</v>
+      </c>
+      <c r="S19">
+        <v>2.4</v>
+      </c>
+      <c r="T19">
+        <v>3.1</v>
+      </c>
+      <c r="U19">
+        <v>1.33</v>
+      </c>
+      <c r="V19">
+        <v>9.5</v>
+      </c>
+      <c r="W19">
+        <v>1.05</v>
+      </c>
+      <c r="X19">
+        <v>1.07</v>
+      </c>
+      <c r="Y19">
+        <v>8.5</v>
+      </c>
+      <c r="Z19">
+        <v>1.41</v>
+      </c>
+      <c r="AA19">
+        <v>2.71</v>
+      </c>
+      <c r="AB19">
+        <v>1.95</v>
+      </c>
+      <c r="AC19">
+        <v>1.75</v>
+      </c>
+      <c r="AD19">
+        <v>4</v>
+      </c>
+      <c r="AE19">
+        <v>1.2</v>
+      </c>
+      <c r="AF19">
+        <v>2.4</v>
+      </c>
+      <c r="AG19">
+        <v>1.49</v>
+      </c>
+      <c r="AH19">
+        <v>10</v>
+      </c>
+      <c r="AI19">
+        <v>1.05</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL19" s="3">
+        <v>45860.83333333334</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38">
+      <c r="A20" s="2">
+        <v>45860</v>
+      </c>
+      <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>95</v>
+      </c>
+      <c r="L20">
+        <v>2.13</v>
+      </c>
+      <c r="M20">
+        <v>2.87</v>
+      </c>
+      <c r="N20">
+        <v>3.33</v>
+      </c>
+      <c r="O20">
+        <v>1.87</v>
+      </c>
+      <c r="P20">
+        <v>6.25</v>
+      </c>
+      <c r="Q20">
+        <v>2.37</v>
+      </c>
+      <c r="R20">
+        <v>1.57</v>
+      </c>
+      <c r="S20">
+        <v>2.25</v>
+      </c>
+      <c r="T20">
+        <v>3.66</v>
+      </c>
+      <c r="U20">
+        <v>1.23</v>
+      </c>
+      <c r="V20">
+        <v>11.5</v>
+      </c>
+      <c r="W20">
+        <v>1.03</v>
+      </c>
+      <c r="X20">
+        <v>1.06</v>
+      </c>
+      <c r="Y20">
+        <v>6.3</v>
+      </c>
+      <c r="Z20">
+        <v>1.48</v>
+      </c>
+      <c r="AA20">
+        <v>2.4</v>
+      </c>
+      <c r="AB20">
+        <v>2.65</v>
+      </c>
+      <c r="AC20">
+        <v>1.42</v>
+      </c>
+      <c r="AD20">
+        <v>4.75</v>
+      </c>
+      <c r="AE20">
+        <v>1.15</v>
+      </c>
+      <c r="AF20">
+        <v>2.1</v>
+      </c>
+      <c r="AG20">
+        <v>1.65</v>
+      </c>
+      <c r="AH20">
+        <v>10</v>
+      </c>
+      <c r="AI20">
+        <v>1.04</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL20" s="3">
+        <v>45860.89583333334</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38">
+      <c r="A21" s="2">
+        <v>45860</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
+        <v>95</v>
+      </c>
+      <c r="L21">
         <v>2.02</v>
       </c>
-      <c r="M8">
+      <c r="M21">
         <v>2.83</v>
       </c>
-      <c r="N8">
+      <c r="N21">
         <v>3.69</v>
       </c>
-      <c r="O8">
+      <c r="O21">
         <v>1.68</v>
       </c>
-      <c r="P8">
+      <c r="P21">
         <v>6.25</v>
       </c>
-      <c r="Q8">
+      <c r="Q21">
         <v>2.75</v>
       </c>
-      <c r="R8">
+      <c r="R21">
+        <v>1.53</v>
+      </c>
+      <c r="S21">
+        <v>2.34</v>
+      </c>
+      <c r="T21">
+        <v>3.48</v>
+      </c>
+      <c r="U21">
+        <v>1.26</v>
+      </c>
+      <c r="V21">
+        <v>9</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>1.11</v>
+      </c>
+      <c r="Y21">
+        <v>6.4</v>
+      </c>
+      <c r="Z21">
         <v>1.5</v>
       </c>
-      <c r="S8">
-        <v>2.34</v>
-      </c>
-      <c r="T8">
-        <v>3.4</v>
-      </c>
-      <c r="U8">
-        <v>1.27</v>
-      </c>
-      <c r="V8">
-        <v>9</v>
-      </c>
-      <c r="W8">
-        <v>1</v>
-      </c>
-      <c r="X8">
-        <v>1.1</v>
-      </c>
-      <c r="Y8">
-        <v>6.5</v>
-      </c>
-      <c r="Z8">
-        <v>1.44</v>
-      </c>
-      <c r="AA8">
-        <v>2.44</v>
-      </c>
-      <c r="AB8">
+      <c r="AA21">
+        <v>2.4</v>
+      </c>
+      <c r="AB21">
         <v>2.3</v>
       </c>
-      <c r="AC8">
+      <c r="AC21">
         <v>1.5</v>
       </c>
-      <c r="AD8">
-        <v>4.5</v>
-      </c>
-      <c r="AE8">
-        <v>1.17</v>
-      </c>
-      <c r="AF8">
-        <v>2.29</v>
-      </c>
-      <c r="AG8">
+      <c r="AD21">
+        <v>5</v>
+      </c>
+      <c r="AE21">
+        <v>1.13</v>
+      </c>
+      <c r="AF21">
+        <v>2.2</v>
+      </c>
+      <c r="AG21">
         <v>1.6</v>
       </c>
-      <c r="AH8">
-        <v>10.5</v>
-      </c>
-      <c r="AI8">
+      <c r="AH21">
+        <v>11</v>
+      </c>
+      <c r="AI21">
         <v>1.05</v>
       </c>
-      <c r="AJ8" t="s">
-        <v>61</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL8" s="3">
+      <c r="AJ21" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL21" s="3">
         <v>45860.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-07-22.xlsx
+++ b/jogos_2025-07-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="121">
   <si>
     <t>Date</t>
   </si>
@@ -172,6 +172,9 @@
     <t>Europe UEFA Champions League</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
@@ -181,39 +184,42 @@
     <t>2025/2026</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Anyang</t>
   </si>
   <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>KuPS</t>
   </si>
   <si>
+    <t>Lincoln Red Imps</t>
+  </si>
+  <si>
     <t>Artsakh</t>
   </si>
   <si>
-    <t>Lincoln Red Imps</t>
+    <t>Egersund</t>
   </si>
   <si>
     <t>København</t>
   </si>
   <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Hamrun Spartans</t>
+  </si>
+  <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
     <t>Paphos</t>
   </si>
   <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Hamrun Spartans</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
     <t>Shkendija</t>
   </si>
   <si>
@@ -223,12 +229,12 @@
     <t>Lech Poznań</t>
   </si>
   <si>
+    <t>Rangers</t>
+  </si>
+  <si>
     <t>Rijeka</t>
   </si>
   <si>
-    <t>Rangers</t>
-  </si>
-  <si>
     <t>Operário PR</t>
   </si>
   <si>
@@ -241,39 +247,42 @@
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Suwon</t>
+  </si>
+  <si>
     <t>Daegu</t>
   </si>
   <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Suwon</t>
-  </si>
-  <si>
     <t>Kairat</t>
   </si>
   <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
     <t>Ferencváros</t>
   </si>
   <si>
-    <t>Red Star Belgrade</t>
+    <t>Aalesund</t>
   </si>
   <si>
     <t>Drita</t>
   </si>
   <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Dynamo Kyiv</t>
+  </si>
+  <si>
+    <t>Malmö FF</t>
+  </si>
+  <si>
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
-    <t>Servette</t>
-  </si>
-  <si>
-    <t>Dynamo Kyiv</t>
-  </si>
-  <si>
-    <t>Malmö FF</t>
-  </si>
-  <si>
     <t>FCSB</t>
   </si>
   <si>
@@ -283,12 +292,12 @@
     <t>Breidablik</t>
   </si>
   <si>
+    <t>Panathinaikos</t>
+  </si>
+  <si>
     <t>Ludogorets</t>
   </si>
   <si>
-    <t>Panathinaikos</t>
-  </si>
-  <si>
     <t>Atlético GO</t>
   </si>
   <si>
@@ -301,10 +310,73 @@
     <t>CRB</t>
   </si>
   <si>
+    <t>complete</t>
+  </si>
+  <si>
     <t>incomplete</t>
   </si>
   <si>
+    <t>['41']</t>
+  </si>
+  <si>
+    <t>['30', '45+4', '82', '90+3']</t>
+  </si>
+  <si>
+    <t>['37']</t>
+  </si>
+  <si>
+    <t>['49', '71']</t>
+  </si>
+  <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['35']</t>
+  </si>
+  <si>
+    <t>['59', '78']</t>
+  </si>
+  <si>
+    <t>['69', '76']</t>
+  </si>
+  <si>
+    <t>['40']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
+    <t>['65']</t>
+  </si>
+  <si>
+    <t>['52', '78']</t>
+  </si>
+  <si>
+    <t>['19', '38', '65', '79', '83']</t>
+  </si>
+  <si>
+    <t>['73']</t>
+  </si>
+  <si>
+    <t>['30']</t>
+  </si>
+  <si>
+    <t>['45', '49']</t>
+  </si>
+  <si>
+    <t>['62', '74']</t>
+  </si>
+  <si>
+    <t>['13']</t>
+  </si>
+  <si>
+    <t>['13', '76', '90+2']</t>
+  </si>
+  <si>
+    <t>['13', '35', '58', '88']</t>
+  </si>
+  <si>
+    <t>['90+10']</t>
   </si>
 </sst>
 </file>
@@ -668,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL21"/>
+  <dimension ref="A1:AL22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -798,106 +870,106 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L2">
         <v>1.9</v>
       </c>
       <c r="M2">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="N2">
         <v>3.45</v>
       </c>
       <c r="O2">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="P2">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q2">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="T2">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="U2">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V2">
+        <v>7.5</v>
+      </c>
+      <c r="W2">
+        <v>1.08</v>
+      </c>
+      <c r="X2">
+        <v>1.06</v>
+      </c>
+      <c r="Y2">
+        <v>8.5</v>
+      </c>
+      <c r="Z2">
+        <v>1.33</v>
+      </c>
+      <c r="AA2">
+        <v>3.25</v>
+      </c>
+      <c r="AB2">
+        <v>1.96</v>
+      </c>
+      <c r="AC2">
+        <v>1.74</v>
+      </c>
+      <c r="AD2">
+        <v>3.5</v>
+      </c>
+      <c r="AE2">
+        <v>1.28</v>
+      </c>
+      <c r="AF2">
+        <v>1.83</v>
+      </c>
+      <c r="AG2">
+        <v>1.85</v>
+      </c>
+      <c r="AH2">
         <v>6.5</v>
       </c>
-      <c r="W2">
+      <c r="AI2">
         <v>1.1</v>
       </c>
-      <c r="X2">
-        <v>1.05</v>
-      </c>
-      <c r="Y2">
-        <v>9</v>
-      </c>
-      <c r="Z2">
-        <v>1.28</v>
-      </c>
-      <c r="AA2">
-        <v>3.6</v>
-      </c>
-      <c r="AB2">
-        <v>1.7</v>
-      </c>
-      <c r="AC2">
-        <v>2.02</v>
-      </c>
-      <c r="AD2">
-        <v>3</v>
-      </c>
-      <c r="AE2">
-        <v>1.34</v>
-      </c>
-      <c r="AF2">
-        <v>1.7</v>
-      </c>
-      <c r="AG2">
-        <v>2</v>
-      </c>
-      <c r="AH2">
-        <v>5.75</v>
-      </c>
-      <c r="AI2">
-        <v>1.12</v>
-      </c>
       <c r="AJ2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AK2" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AL2" s="3">
         <v>45860.3125</v>
@@ -914,106 +986,106 @@
         <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L3">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="M3">
-        <v>3.06</v>
+        <v>3.32</v>
       </c>
       <c r="N3">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="O3">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="P3">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q3">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="R3">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S3">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="T3">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U3">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V3">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Z3">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AA3">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AB3">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="AD3">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AE3">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AF3">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG3">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH3">
-        <v>6.66</v>
+        <v>5.75</v>
       </c>
       <c r="AI3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="AK3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AL3" s="3">
         <v>45860.3125</v>
@@ -1030,61 +1102,61 @@
         <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L4">
-        <v>1.9</v>
+        <v>2.56</v>
       </c>
       <c r="M4">
-        <v>3.29</v>
+        <v>3.06</v>
       </c>
       <c r="N4">
-        <v>3.45</v>
+        <v>2.48</v>
       </c>
       <c r="O4">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="P4">
         <v>8.5</v>
       </c>
       <c r="Q4">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="R4">
         <v>1.4</v>
       </c>
       <c r="S4">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="T4">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V4">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>1.08</v>
@@ -1096,40 +1168,40 @@
         <v>8.5</v>
       </c>
       <c r="Z4">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AA4">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AB4">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AC4">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AD4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AE4">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF4">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH4">
-        <v>6.5</v>
+        <v>6.66</v>
       </c>
       <c r="AI4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="AK4" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AL4" s="3">
         <v>45860.3125</v>
@@ -1146,16 +1218,16 @@
         <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1167,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L5">
         <v>2.5</v>
@@ -1218,10 +1290,10 @@
         <v>2.83</v>
       </c>
       <c r="AB5">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AD5">
         <v>3.95</v>
@@ -1242,10 +1314,10 @@
         <v>1.02</v>
       </c>
       <c r="AJ5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AL5" s="3">
         <v>45860.5</v>
@@ -1262,106 +1334,106 @@
         <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L6">
-        <v>3.1</v>
+        <v>11</v>
       </c>
       <c r="M6">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="O6">
-        <v>2.2</v>
+        <v>4.75</v>
       </c>
       <c r="P6">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
       <c r="Q6">
-        <v>1.82</v>
+        <v>1.23</v>
       </c>
       <c r="R6">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S6">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="T6">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="U6">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="V6">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>8.5</v>
+        <v>17</v>
       </c>
       <c r="Z6">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AA6">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="AB6">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AC6">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AD6">
-        <v>3.4</v>
+        <v>2.02</v>
       </c>
       <c r="AE6">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="AF6">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="AG6">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AH6">
-        <v>6.75</v>
+        <v>4.3</v>
       </c>
       <c r="AI6">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AJ6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AK6" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="AL6" s="3">
         <v>45860.54166666666</v>
@@ -1378,106 +1450,106 @@
         <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L7">
-        <v>11</v>
+        <v>3.1</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="N7">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="O7">
-        <v>4.75</v>
+        <v>2.2</v>
       </c>
       <c r="P7">
-        <v>13.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q7">
-        <v>1.23</v>
+        <v>1.82</v>
       </c>
       <c r="R7">
+        <v>1.4</v>
+      </c>
+      <c r="S7">
+        <v>2.7</v>
+      </c>
+      <c r="T7">
+        <v>2.85</v>
+      </c>
+      <c r="U7">
+        <v>1.37</v>
+      </c>
+      <c r="V7">
+        <v>7.5</v>
+      </c>
+      <c r="W7">
+        <v>1.08</v>
+      </c>
+      <c r="X7">
+        <v>1.06</v>
+      </c>
+      <c r="Y7">
+        <v>8.5</v>
+      </c>
+      <c r="Z7">
+        <v>1.32</v>
+      </c>
+      <c r="AA7">
+        <v>3.1</v>
+      </c>
+      <c r="AB7">
+        <v>2.05</v>
+      </c>
+      <c r="AC7">
+        <v>1.73</v>
+      </c>
+      <c r="AD7">
+        <v>3.4</v>
+      </c>
+      <c r="AE7">
         <v>1.28</v>
       </c>
-      <c r="S7">
-        <v>3.4</v>
-      </c>
-      <c r="T7">
-        <v>2.25</v>
-      </c>
-      <c r="U7">
-        <v>1.55</v>
-      </c>
-      <c r="V7">
-        <v>5.25</v>
-      </c>
-      <c r="W7">
-        <v>1.14</v>
-      </c>
-      <c r="X7">
-        <v>1.01</v>
-      </c>
-      <c r="Y7">
-        <v>17</v>
-      </c>
-      <c r="Z7">
-        <v>1.14</v>
-      </c>
-      <c r="AA7">
-        <v>4.33</v>
-      </c>
-      <c r="AB7">
-        <v>1.53</v>
-      </c>
-      <c r="AC7">
-        <v>2.4</v>
-      </c>
-      <c r="AD7">
-        <v>2.34</v>
-      </c>
-      <c r="AE7">
-        <v>1.6</v>
-      </c>
       <c r="AF7">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AG7">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AH7">
-        <v>4.3</v>
+        <v>6.75</v>
       </c>
       <c r="AI7">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AJ7" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="AL7" s="3">
         <v>45860.54166666666</v>
@@ -1488,25 +1560,25 @@
         <v>45860</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
         <v>54</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1515,88 +1587,88 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L8">
+        <v>2.71</v>
+      </c>
+      <c r="M8">
+        <v>3.45</v>
+      </c>
+      <c r="N8">
+        <v>2.49</v>
+      </c>
+      <c r="O8">
+        <v>2</v>
+      </c>
+      <c r="P8">
+        <v>12.5</v>
+      </c>
+      <c r="Q8">
+        <v>1.8</v>
+      </c>
+      <c r="R8">
+        <v>1.3</v>
+      </c>
+      <c r="S8">
+        <v>3.4</v>
+      </c>
+      <c r="T8">
+        <v>2.38</v>
+      </c>
+      <c r="U8">
+        <v>1.53</v>
+      </c>
+      <c r="V8">
+        <v>6</v>
+      </c>
+      <c r="W8">
         <v>1.13</v>
       </c>
-      <c r="M8">
-        <v>7.6</v>
-      </c>
-      <c r="N8">
-        <v>18</v>
-      </c>
-      <c r="O8">
-        <v>1.13</v>
-      </c>
-      <c r="P8">
-        <v>18.5</v>
-      </c>
-      <c r="Q8">
-        <v>6</v>
-      </c>
-      <c r="R8">
-        <v>1.2</v>
-      </c>
-      <c r="S8">
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>11.5</v>
+      </c>
+      <c r="Z8">
+        <v>1.17</v>
+      </c>
+      <c r="AA8">
+        <v>4.05</v>
+      </c>
+      <c r="AB8">
+        <v>1.76</v>
+      </c>
+      <c r="AC8">
+        <v>1.93</v>
+      </c>
+      <c r="AD8">
+        <v>2.39</v>
+      </c>
+      <c r="AE8">
+        <v>1.43</v>
+      </c>
+      <c r="AF8">
+        <v>1.53</v>
+      </c>
+      <c r="AG8">
+        <v>2.38</v>
+      </c>
+      <c r="AH8">
         <v>4.33</v>
       </c>
-      <c r="T8">
-        <v>1.91</v>
-      </c>
-      <c r="U8">
-        <v>1.8</v>
-      </c>
-      <c r="V8">
-        <v>4</v>
-      </c>
-      <c r="W8">
-        <v>1.22</v>
-      </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
-      <c r="Y8">
-        <v>19</v>
-      </c>
-      <c r="Z8">
-        <v>1.12</v>
-      </c>
-      <c r="AA8">
-        <v>5.47</v>
-      </c>
-      <c r="AB8">
-        <v>1.42</v>
-      </c>
-      <c r="AC8">
-        <v>2.75</v>
-      </c>
-      <c r="AD8">
-        <v>1.95</v>
-      </c>
-      <c r="AE8">
-        <v>1.65</v>
-      </c>
-      <c r="AF8">
-        <v>2.25</v>
-      </c>
-      <c r="AG8">
-        <v>1.57</v>
-      </c>
-      <c r="AH8">
-        <v>3.02</v>
-      </c>
       <c r="AI8">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AJ8" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="AK8" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="AL8" s="3">
-        <v>45860.58333333334</v>
+        <v>45860.54166666666</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1610,16 +1682,16 @@
         <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1631,85 +1703,85 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L9">
-        <v>2.13</v>
+        <v>1.13</v>
       </c>
       <c r="M9">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="N9">
-        <v>3.3</v>
+        <v>18</v>
       </c>
       <c r="O9">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="P9">
-        <v>9.5</v>
+        <v>18.5</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="T9">
+        <v>1.91</v>
+      </c>
+      <c r="U9">
+        <v>1.8</v>
+      </c>
+      <c r="V9">
+        <v>4</v>
+      </c>
+      <c r="W9">
+        <v>1.22</v>
+      </c>
+      <c r="X9">
+        <v>1.01</v>
+      </c>
+      <c r="Y9">
+        <v>19</v>
+      </c>
+      <c r="Z9">
+        <v>1.12</v>
+      </c>
+      <c r="AA9">
+        <v>5.47</v>
+      </c>
+      <c r="AB9">
+        <v>1.42</v>
+      </c>
+      <c r="AC9">
         <v>2.75</v>
       </c>
-      <c r="U9">
-        <v>1.4</v>
-      </c>
-      <c r="V9">
-        <v>6.5</v>
-      </c>
-      <c r="W9">
-        <v>1.1</v>
-      </c>
-      <c r="X9">
-        <v>1.04</v>
-      </c>
-      <c r="Y9">
-        <v>9</v>
-      </c>
-      <c r="Z9">
-        <v>1.22</v>
-      </c>
-      <c r="AA9">
-        <v>3.9</v>
-      </c>
-      <c r="AB9">
-        <v>1.88</v>
-      </c>
-      <c r="AC9">
-        <v>1.72</v>
-      </c>
       <c r="AD9">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AE9">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AF9">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AG9">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AH9">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="AI9">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AJ9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="AK9" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AL9" s="3">
         <v>45860.58333333334</v>
@@ -1726,28 +1798,28 @@
         <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L10">
         <v>1.77</v>
@@ -1822,10 +1894,10 @@
         <v>1.09</v>
       </c>
       <c r="AJ10" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AK10" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="AL10" s="3">
         <v>45860.58333333334</v>
@@ -1842,28 +1914,28 @@
         <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L11">
         <v>7</v>
@@ -1938,10 +2010,10 @@
         <v>1.2</v>
       </c>
       <c r="AJ11" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="AL11" s="3">
         <v>45860.58333333334</v>
@@ -1958,28 +2030,28 @@
         <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L12">
         <v>3.75</v>
@@ -2054,10 +2126,10 @@
         <v>1.03</v>
       </c>
       <c r="AJ12" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="AK12" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="AL12" s="3">
         <v>45860.58333333334</v>
@@ -2068,25 +2140,25 @@
         <v>45860</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
         <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2095,88 +2167,88 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L13">
-        <v>3.6</v>
+        <v>2.13</v>
       </c>
       <c r="M13">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N13">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="O13">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="P13">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="Q13">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="R13">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S13">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="T13">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="U13">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="V13">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>7.25</v>
+        <v>9</v>
       </c>
       <c r="Z13">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AA13">
+        <v>3.9</v>
+      </c>
+      <c r="AB13">
+        <v>1.88</v>
+      </c>
+      <c r="AC13">
+        <v>1.72</v>
+      </c>
+      <c r="AD13">
         <v>2.75</v>
       </c>
-      <c r="AB13">
-        <v>2.2</v>
-      </c>
-      <c r="AC13">
-        <v>1.61</v>
-      </c>
-      <c r="AD13">
+      <c r="AE13">
+        <v>1.42</v>
+      </c>
+      <c r="AF13">
+        <v>1.8</v>
+      </c>
+      <c r="AG13">
+        <v>1.91</v>
+      </c>
+      <c r="AH13">
         <v>4</v>
       </c>
-      <c r="AE13">
+      <c r="AI13">
         <v>1.22</v>
       </c>
-      <c r="AF13">
-        <v>1.98</v>
-      </c>
-      <c r="AG13">
-        <v>1.73</v>
-      </c>
-      <c r="AH13">
-        <v>8.25</v>
-      </c>
-      <c r="AI13">
-        <v>1.07</v>
-      </c>
       <c r="AJ13" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="AK13" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="AL13" s="3">
-        <v>45860.625</v>
+        <v>45860.58333333334</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2184,22 +2256,22 @@
         <v>45860</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
         <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2211,88 +2283,88 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L14">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M14">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N14">
-        <v>4.4</v>
+        <v>2.05</v>
       </c>
       <c r="O14">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="P14">
-        <v>9.25</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>2.65</v>
+        <v>1.75</v>
       </c>
       <c r="R14">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="S14">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="T14">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="U14">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="V14">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="W14">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y14">
-        <v>9.5</v>
+        <v>7.25</v>
       </c>
       <c r="Z14">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AA14">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AB14">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AC14">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AD14">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AE14">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AF14">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AG14">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AH14">
-        <v>5.75</v>
+        <v>8.25</v>
       </c>
       <c r="AI14">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AJ14" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="AK14" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AL14" s="3">
-        <v>45860.63541666666</v>
+        <v>45860.625</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2300,19 +2372,19 @@
         <v>45860</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
         <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2327,88 +2399,88 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L15">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M15">
+        <v>3.5</v>
+      </c>
+      <c r="N15">
+        <v>4.4</v>
+      </c>
+      <c r="O15">
+        <v>1.58</v>
+      </c>
+      <c r="P15">
+        <v>9.25</v>
+      </c>
+      <c r="Q15">
+        <v>2.65</v>
+      </c>
+      <c r="R15">
+        <v>1.36</v>
+      </c>
+      <c r="S15">
+        <v>2.85</v>
+      </c>
+      <c r="T15">
+        <v>2.65</v>
+      </c>
+      <c r="U15">
+        <v>1.42</v>
+      </c>
+      <c r="V15">
         <v>6.5</v>
       </c>
-      <c r="N15">
-        <v>6</v>
-      </c>
-      <c r="O15">
-        <v>1.31</v>
-      </c>
-      <c r="P15">
-        <v>15</v>
-      </c>
-      <c r="Q15">
-        <v>3.7</v>
-      </c>
-      <c r="R15">
-        <v>1.24</v>
-      </c>
-      <c r="S15">
-        <v>3.6</v>
-      </c>
-      <c r="T15">
-        <v>2.15</v>
-      </c>
-      <c r="U15">
-        <v>1.61</v>
-      </c>
-      <c r="V15">
-        <v>4.8</v>
-      </c>
       <c r="W15">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>15.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z15">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AA15">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB15">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="AC15">
-        <v>2.27</v>
+        <v>1.82</v>
       </c>
       <c r="AD15">
-        <v>2.15</v>
+        <v>3.55</v>
       </c>
       <c r="AE15">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="AF15">
+        <v>1.8</v>
+      </c>
+      <c r="AG15">
         <v>1.88</v>
       </c>
-      <c r="AG15">
-        <v>1.8</v>
-      </c>
       <c r="AH15">
-        <v>3.9</v>
+        <v>5.75</v>
       </c>
       <c r="AI15">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AJ15" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AK15" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AL15" s="3">
-        <v>45860.64583333334</v>
+        <v>45860.63541666666</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2416,19 +2488,19 @@
         <v>45860</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2443,88 +2515,88 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L16">
-        <v>2.22</v>
+        <v>1.3</v>
       </c>
       <c r="M16">
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
       <c r="N16">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>1.83</v>
+        <v>1.31</v>
       </c>
       <c r="P16">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="Q16">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="R16">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="S16">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="T16">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="U16">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="W16">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X16">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z16">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AA16">
-        <v>2.87</v>
+        <v>4.75</v>
       </c>
       <c r="AB16">
-        <v>2.29</v>
+        <v>1.56</v>
       </c>
       <c r="AC16">
-        <v>1.55</v>
+        <v>2.27</v>
       </c>
       <c r="AD16">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="AE16">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AF16">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG16">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH16">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="AI16">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AJ16" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AK16" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AL16" s="3">
-        <v>45860.65625</v>
+        <v>45860.64583333334</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2538,16 +2610,16 @@
         <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2559,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L17">
         <v>1.87</v>
@@ -2634,10 +2706,10 @@
         <v>1.18</v>
       </c>
       <c r="AJ17" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="AK17" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AL17" s="3">
         <v>45860.65625</v>
@@ -2648,19 +2720,19 @@
         <v>45860</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2675,88 +2747,88 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L18">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="M18">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="N18">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="O18">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="P18">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q18">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R18">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="S18">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="T18">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="U18">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y18">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Z18">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AA18">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="AB18">
-        <v>2.65</v>
+        <v>2.29</v>
       </c>
       <c r="AC18">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AD18">
-        <v>5.93</v>
+        <v>3.7</v>
       </c>
       <c r="AE18">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AF18">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AG18">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AH18">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="AI18">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AJ18" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AK18" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AL18" s="3">
-        <v>45860.79166666666</v>
+        <v>45860.65625</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2764,19 +2836,19 @@
         <v>45860</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2791,88 +2863,88 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L19">
-        <v>1.45</v>
+        <v>2.65</v>
       </c>
       <c r="M19">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="N19">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="O19">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="P19">
-        <v>8.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q19">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="R19">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="S19">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="T19">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="U19">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V19">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y19">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="Z19">
+        <v>1.6</v>
+      </c>
+      <c r="AA19">
+        <v>2.35</v>
+      </c>
+      <c r="AB19">
+        <v>2.85</v>
+      </c>
+      <c r="AC19">
         <v>1.41</v>
       </c>
-      <c r="AA19">
-        <v>2.71</v>
-      </c>
-      <c r="AB19">
-        <v>1.95</v>
-      </c>
-      <c r="AC19">
-        <v>1.75</v>
-      </c>
       <c r="AD19">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AG19">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AH19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI19">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ19" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AK19" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AL19" s="3">
-        <v>45860.83333333334</v>
+        <v>45860.79166666666</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2880,19 +2952,19 @@
         <v>45860</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2907,88 +2979,88 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L20">
-        <v>2.13</v>
+        <v>1.48</v>
       </c>
       <c r="M20">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="N20">
-        <v>3.33</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>1.87</v>
+        <v>1.39</v>
       </c>
       <c r="P20">
-        <v>6.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q20">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="R20">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S20">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="T20">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="U20">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="V20">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y20">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="Z20">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AA20">
+        <v>2.5</v>
+      </c>
+      <c r="AB20">
         <v>2.4</v>
       </c>
-      <c r="AB20">
-        <v>2.65</v>
-      </c>
       <c r="AC20">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AD20">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AE20">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF20">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AG20">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AH20">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AI20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AK20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AL20" s="3">
-        <v>45860.89583333334</v>
+        <v>45860.83333333334</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -2996,19 +3068,19 @@
         <v>45860</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3023,87 +3095,203 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L21">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="M21">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="N21">
-        <v>3.69</v>
+        <v>3.45</v>
       </c>
       <c r="O21">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="P21">
         <v>6.25</v>
       </c>
       <c r="Q21">
+        <v>2.37</v>
+      </c>
+      <c r="R21">
+        <v>1.65</v>
+      </c>
+      <c r="S21">
+        <v>2.28</v>
+      </c>
+      <c r="T21">
+        <v>3.6</v>
+      </c>
+      <c r="U21">
+        <v>1.25</v>
+      </c>
+      <c r="V21">
+        <v>10.5</v>
+      </c>
+      <c r="W21">
+        <v>1.05</v>
+      </c>
+      <c r="X21">
+        <v>1.15</v>
+      </c>
+      <c r="Y21">
+        <v>5.5</v>
+      </c>
+      <c r="Z21">
+        <v>1.6</v>
+      </c>
+      <c r="AA21">
+        <v>2.25</v>
+      </c>
+      <c r="AB21">
+        <v>2.8</v>
+      </c>
+      <c r="AC21">
+        <v>1.4</v>
+      </c>
+      <c r="AD21">
+        <v>5.5</v>
+      </c>
+      <c r="AE21">
+        <v>1.11</v>
+      </c>
+      <c r="AF21">
+        <v>2.24</v>
+      </c>
+      <c r="AG21">
+        <v>1.58</v>
+      </c>
+      <c r="AH21">
+        <v>10</v>
+      </c>
+      <c r="AI21">
+        <v>1.03</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>104</v>
+      </c>
+      <c r="AL21" s="3">
+        <v>45860.89583333334</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38">
+      <c r="A22" s="2">
+        <v>45860</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>99</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
+      </c>
+      <c r="M22">
+        <v>3</v>
+      </c>
+      <c r="N22">
+        <v>3.85</v>
+      </c>
+      <c r="O22">
+        <v>1.68</v>
+      </c>
+      <c r="P22">
+        <v>6.25</v>
+      </c>
+      <c r="Q22">
         <v>2.75</v>
       </c>
-      <c r="R21">
-        <v>1.53</v>
-      </c>
-      <c r="S21">
+      <c r="R22">
+        <v>1.5</v>
+      </c>
+      <c r="S22">
         <v>2.34</v>
       </c>
-      <c r="T21">
-        <v>3.48</v>
-      </c>
-      <c r="U21">
-        <v>1.26</v>
-      </c>
-      <c r="V21">
-        <v>9</v>
-      </c>
-      <c r="W21">
+      <c r="T22">
+        <v>3.5</v>
+      </c>
+      <c r="U22">
+        <v>1.29</v>
+      </c>
+      <c r="V22">
+        <v>11</v>
+      </c>
+      <c r="W22">
         <v>1</v>
       </c>
-      <c r="X21">
+      <c r="X22">
         <v>1.11</v>
       </c>
-      <c r="Y21">
-        <v>6.4</v>
-      </c>
-      <c r="Z21">
+      <c r="Y22">
+        <v>6.5</v>
+      </c>
+      <c r="Z22">
+        <v>1.44</v>
+      </c>
+      <c r="AA22">
+        <v>2.65</v>
+      </c>
+      <c r="AB22">
+        <v>2.52</v>
+      </c>
+      <c r="AC22">
         <v>1.5</v>
       </c>
-      <c r="AA21">
-        <v>2.4</v>
-      </c>
-      <c r="AB21">
-        <v>2.3</v>
-      </c>
-      <c r="AC21">
-        <v>1.5</v>
-      </c>
-      <c r="AD21">
-        <v>5</v>
-      </c>
-      <c r="AE21">
-        <v>1.13</v>
-      </c>
-      <c r="AF21">
-        <v>2.2</v>
-      </c>
-      <c r="AG21">
-        <v>1.6</v>
-      </c>
-      <c r="AH21">
+      <c r="AD22">
+        <v>4.7</v>
+      </c>
+      <c r="AE22">
+        <v>1.12</v>
+      </c>
+      <c r="AF22">
+        <v>2.12</v>
+      </c>
+      <c r="AG22">
+        <v>1.66</v>
+      </c>
+      <c r="AH22">
         <v>11</v>
       </c>
-      <c r="AI21">
+      <c r="AI22">
         <v>1.05</v>
       </c>
-      <c r="AJ21" t="s">
-        <v>96</v>
-      </c>
-      <c r="AK21" t="s">
-        <v>96</v>
-      </c>
-      <c r="AL21" s="3">
+      <c r="AJ22" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>104</v>
+      </c>
+      <c r="AL22" s="3">
         <v>45860.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-07-22.xlsx
+++ b/jogos_2025-07-22.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3.06</v>
+        <v>3.29</v>
       </c>
       <c r="N2" t="n">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V2" t="n">
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['19', '38', '65', '79', '83']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45860.3125</v>
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.9</v>
+        <v>2.56</v>
       </c>
       <c r="M3" t="n">
-        <v>3.29</v>
+        <v>3.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>2.48</v>
       </c>
       <c r="O3" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
         <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
         <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['19', '38', '65', '79', '83']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45860.3125</v>
@@ -1149,119 +1149,119 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.06</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.4</v>
+        <v>2.39</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['59', '78']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['45', '49']</t>
+          <t>['62', '74']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45860.54166666666</v>
@@ -1278,35 +1278,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X7" t="n">
         <v>3.1</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="Y7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA7" t="n">
         <v>3.4</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AB7" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['59', '78']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['62', '74']</t>
+          <t>['45', '49']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AI7" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45860.54166666666</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,55 +1572,55 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="O9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T9" t="n">
         <v>2.63</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
         <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
         <v>1.8</v>
@@ -1630,25 +1630,25 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['90+10']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45860.58333333334</v>
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>7</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="O11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AC11" t="n">
         <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['13', '76', '90+2']</t>
+          <t>['90+10']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>2.75</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.38</v>
+        <v>2.4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45860.58333333334</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.77</v>
+        <v>1.13</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="O12" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>12</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>3.8</v>
+        <v>5.47</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="Z12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA12" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA12" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
+          <t>['69', '76']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['13']</t>
-        </is>
-      </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.15</v>
+        <v>6.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45860.58333333334</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.13</v>
+        <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="N13" t="n">
-        <v>18</v>
+        <v>1.41</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>1.87</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X13" t="n">
         <v>4.33</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="Y13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1.8</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AD13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['13', '76', '90+2']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
         <v>2.75</v>
       </c>
-      <c r="AA13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['69', '76']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AH13" t="n">
-        <v>6.75</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.13</v>
+        <v>3.25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>6</v>
+        <v>1.38</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45860.58333333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,16 +2965,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T20" t="n">
         <v>3.4</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="X20" t="n">
-        <v>3.65</v>
+        <v>2.44</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.95</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45860.83333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,16 +3094,16 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.42</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="U21" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>2.44</v>
+        <v>3.65</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>5</v>
+        <v>2.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45860.83333333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="O22" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.6</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>2.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.63</v>
+        <v>1.42</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.1</v>
+        <v>5.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>1.12</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['27', '38', '66']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['45+4', '69']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45860.89583333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="M23" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="P23" t="n">
-        <v>1.76</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['27', '38', '66']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['45+4', '69']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>2.4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['18']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['37']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>2.37</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45860.89583333334</v>
